--- a/Datos limpios/Pricing semanal/2025/Sorgo.xlsx
+++ b/Datos limpios/Pricing semanal/2025/Sorgo.xlsx
@@ -2280,298 +2280,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D6CA5EAACE9DA04D9E421A617A76D009" ma:contentTypeVersion="19" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="854b0670eee28d8fa271d4f22cb9c97d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77131357-5c03-45fa-a80b-b9111bb46cb1" xmlns:ns3="d3f11db4-a96c-41b4-b8ec-902c72f52048" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b486ba09ce8a2fb19cc660d7edf32df4" ns2:_="" ns3:_="">
-    <xsd:import namespace="77131357-5c03-45fa-a80b-b9111bb46cb1"/>
-    <xsd:import namespace="d3f11db4-a96c-41b4-b8ec-902c72f52048"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="77131357-5c03-45fa-a80b-b9111bb46cb1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_Flow_SignoffStatus" ma:index="20" nillable="true" ma:displayName="Estado de aprobación" ma:internalName="Estado_x0020_de_x0020_aprobaci_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6ab20cb4-9c0f-41d2-89f3-02c382a657d6" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="25" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="26" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d3f11db4-a96c-41b4-b8ec-902c72f52048" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="24" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ac6aff7b-77d9-4645-af3f-7b0008d975fa}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d3f11db4-a96c-41b4-b8ec-902c72f52048">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1" xsi:nil="true"/>
-    <TaxCatchAll xmlns="d3f11db4-a96c-41b4-b8ec-902c72f52048" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E71A9C4A-2E87-4DC3-87F5-110E040FBD14}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D49BE33D-7470-4E65-8962-356E767C374F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC169A61-EF5C-45AB-8932-C6C93C760543}"/>
 </file>
--- a/Datos limpios/Pricing semanal/2025/Sorgo.xlsx
+++ b/Datos limpios/Pricing semanal/2025/Sorgo.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
@@ -2202,16 +2202,16 @@
         <v>45943</v>
       </c>
       <c r="D43">
-        <v>22180.73</v>
+        <v>21680.73</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G43">
-        <v>21680.73</v>
+        <v>20680.73</v>
       </c>
       <c r="H43">
         <v>958.13</v>
@@ -2226,7 +2226,7 @@
         <v>958.13</v>
       </c>
       <c r="L43">
-        <v>22638.86</v>
+        <v>21638.86</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -2272,6 +2272,178 @@
         <v>7764.790000000001</v>
       </c>
       <c r="M44" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2025</v>
+      </c>
+      <c r="B45">
+        <v>44</v>
+      </c>
+      <c r="C45" s="2">
+        <v>45957</v>
+      </c>
+      <c r="D45">
+        <v>4707.66</v>
+      </c>
+      <c r="E45">
+        <v>59.86</v>
+      </c>
+      <c r="F45">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="G45">
+        <v>4766.74</v>
+      </c>
+      <c r="H45">
+        <v>8595.26</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>300</v>
+      </c>
+      <c r="K45">
+        <v>8295.26</v>
+      </c>
+      <c r="L45">
+        <v>13062</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2025</v>
+      </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
+      <c r="C46" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D46">
+        <v>4676.16</v>
+      </c>
+      <c r="E46">
+        <v>511.44</v>
+      </c>
+      <c r="F46">
+        <v>30</v>
+      </c>
+      <c r="G46">
+        <v>5157.599999999999</v>
+      </c>
+      <c r="H46">
+        <v>8035.45</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>8035.45</v>
+      </c>
+      <c r="L46">
+        <v>13193.05</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2025</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+      <c r="C47" s="2">
+        <v>45971</v>
+      </c>
+      <c r="D47">
+        <v>4929.81</v>
+      </c>
+      <c r="E47">
+        <v>106.67</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>5036.48</v>
+      </c>
+      <c r="H47">
+        <v>2704.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>2704.3</v>
+      </c>
+      <c r="L47">
+        <v>7740.780000000001</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2025</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48" s="2">
+        <v>45978</v>
+      </c>
+      <c r="D48">
+        <v>2590.8</v>
+      </c>
+      <c r="E48">
+        <v>120</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>2710.8</v>
+      </c>
+      <c r="H48">
+        <v>1003.34</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>1003.34</v>
+      </c>
+      <c r="L48">
+        <v>3714.14</v>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>SORGO</t>
         </is>
